--- a/content/post/drafts/season-prediction/men_simple-model-tests-actual_mae.xlsx
+++ b/content/post/drafts/season-prediction/men_simple-model-tests-actual_mae.xlsx
@@ -610,25 +610,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.133664052067128</v>
+        <v>0.134860348199304</v>
       </c>
       <c r="C9" t="n">
-        <v>0.109401870107805</v>
+        <v>0.109677203278343</v>
       </c>
       <c r="D9" t="n">
-        <v>0.179579693290922</v>
+        <v>0.177284373342045</v>
       </c>
       <c r="E9" t="n">
-        <v>0.148128370812814</v>
+        <v>0.152473361618482</v>
       </c>
       <c r="F9" t="n">
-        <v>0.14535322156992</v>
+        <v>0.143695337595763</v>
       </c>
       <c r="G9" t="n">
-        <v>0.125995166945511</v>
+        <v>0.127396785088524</v>
       </c>
       <c r="H9" t="n">
-        <v>0.14035372913235</v>
+        <v>0.14089790152041</v>
       </c>
     </row>
     <row r="10">
